--- a/docs/game/items-zh_CN.xlsx
+++ b/docs/game/items-zh_CN.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="430">
   <si>
     <t>物品名称</t>
   </si>
@@ -1437,6 +1437,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>一种大号的甜品，松软醇甜（回味无穷）。/生日快乐|ू</t>
     </r>
     <r>
@@ -1532,6 +1538,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>小鱼经过加工之后的产物。</t>
     </r>
     <r>
@@ -1616,6 +1628,15 @@
     <t>小小的蛋糕，大大的温暖。</t>
   </si>
   <si>
+    <t>水煮肉片</t>
+  </si>
+  <si>
+    <t>在熬煮过程中变得鲜香可口（嫩滑爽口）的肉片</t>
+  </si>
+  <si>
+    <t>古语有云，水煮肉片，水加多者为肉片汤，水加少者为滑肉。</t>
+  </si>
+  <si>
     <t>草鱼</t>
   </si>
   <si>
@@ -2088,6 +2109,39 @@
   </si>
   <si>
     <t>（打开）（另附文件）</t>
+  </si>
+  <si>
+    <t>番茄种子</t>
+  </si>
+  <si>
+    <t>农作物的种子。拥有生长的潜力</t>
+  </si>
+  <si>
+    <t>相信某天播下的种子，会在未来发芽。</t>
+  </si>
+  <si>
+    <t>黄瓜种子</t>
+  </si>
+  <si>
+    <t>土豆种子</t>
+  </si>
+  <si>
+    <t>白菜种子</t>
+  </si>
+  <si>
+    <t>胡萝卜种子</t>
+  </si>
+  <si>
+    <t>茄子种子</t>
+  </si>
+  <si>
+    <t>草莓种子</t>
+  </si>
+  <si>
+    <t>水稻种子</t>
+  </si>
+  <si>
+    <t>西瓜种子</t>
   </si>
 </sst>
 </file>
@@ -2733,7 +2787,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2792,13 +2846,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3119,7 +3176,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D130"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="18.4818181818182" style="1" customWidth="1"/>
@@ -3255,7 +3312,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" ht="28" spans="1:4">
+    <row r="12" spans="1:4">
       <c r="A12" s="11" t="s">
         <v>33</v>
       </c>
@@ -3401,7 +3458,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" ht="196" spans="1:4">
+    <row r="25" ht="154" spans="1:4">
       <c r="A25" s="3" t="s">
         <v>72</v>
       </c>
@@ -3479,7 +3536,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="31" ht="42" spans="1:4">
+    <row r="31" ht="28" spans="1:4">
       <c r="A31" s="2" t="s">
         <v>94</v>
       </c>
@@ -3501,7 +3558,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="33" ht="98" spans="1:4">
+    <row r="33" ht="84" spans="1:4">
       <c r="A33" s="3" t="s">
         <v>100</v>
       </c>
@@ -3509,7 +3566,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="34" ht="42" spans="1:4">
+    <row r="34" ht="28" spans="1:4">
       <c r="A34" s="2" t="s">
         <v>102</v>
       </c>
@@ -3534,7 +3591,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" ht="28" spans="1:4">
+    <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
         <v>109</v>
       </c>
@@ -3606,7 +3663,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" ht="56" spans="1:4">
+    <row r="42" ht="42" spans="1:4">
       <c r="A42" s="2" t="s">
         <v>129</v>
       </c>
@@ -3662,7 +3719,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="46" ht="28" spans="1:4">
+    <row r="46" spans="1:4">
       <c r="A46" s="2" t="s">
         <v>145</v>
       </c>
@@ -3744,7 +3801,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="52" ht="42" spans="1:4">
+    <row r="52" ht="28" spans="1:4">
       <c r="A52" s="2" t="s">
         <v>168</v>
       </c>
@@ -4274,7 +4331,7 @@
       <c r="C95" t="s">
         <v>301</v>
       </c>
-      <c r="D95" s="19" t="s">
+      <c r="D95" s="16" t="s">
         <v>302</v>
       </c>
     </row>
@@ -4324,21 +4381,20 @@
       <c r="C99" t="s">
         <v>315</v>
       </c>
-      <c r="D99" s="16" t="s">
-        <v>316</v>
-      </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="C100" t="s">
         <v>318</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" s="16" t="s">
         <v>319</v>
       </c>
-      <c r="D100" s="16"/>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2" t="s">
@@ -4436,26 +4492,26 @@
       </c>
       <c r="D108" s="16"/>
     </row>
-    <row r="109" ht="28" spans="1:4">
+    <row r="109" spans="1:4">
       <c r="A109" s="2" t="s">
         <v>344</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C109" s="20" t="s">
+      <c r="C109" t="s">
         <v>346</v>
       </c>
       <c r="D109" s="16"/>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" ht="28" spans="1:4">
       <c r="A110" s="2" t="s">
         <v>347</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="12" t="s">
         <v>349</v>
       </c>
       <c r="D110" s="16"/>
@@ -4482,82 +4538,83 @@
       <c r="C112" t="s">
         <v>355</v>
       </c>
+      <c r="D112" s="16"/>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B113" s="2" t="s">
         <v>357</v>
       </c>
       <c r="C113" t="s">
         <v>358</v>
       </c>
-      <c r="D113" s="2" t="s">
-        <v>359</v>
-      </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="C114" t="s">
         <v>361</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D114" s="1" t="s">
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="2" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="115" ht="42" spans="1:4">
-      <c r="A115" s="2" t="s">
+      <c r="B115" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="C115" t="s">
         <v>365</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="D115" s="16" t="s">
+    </row>
+    <row r="116" ht="42" spans="1:4">
+      <c r="A116" s="2" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="116" spans="1:4">
-      <c r="A116" s="2" t="s">
+      <c r="B116" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="C116" t="s">
         <v>369</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" s="16" t="s">
         <v>370</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="C117" t="s">
         <v>373</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="D117" s="2" t="s">
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="2" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="118" spans="1:4">
-      <c r="A118" s="3" t="s">
+      <c r="B118" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="C118" t="s">
         <v>377</v>
       </c>
       <c r="D118" s="2" t="s">
@@ -4565,58 +4622,57 @@
       </c>
     </row>
     <row r="119" spans="1:4">
-      <c r="A119" s="2" t="s">
+      <c r="A119" s="3" t="s">
         <v>379</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C119" s="12" t="s">
+      <c r="D119" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B120" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="C120" s="12" t="s">
         <v>384</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B121" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="C121" t="s">
         <v>388</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="D121" s="21" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="C122" t="s">
         <v>392</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" s="19" t="s">
         <v>393</v>
       </c>
-      <c r="D122" s="21"/>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2" t="s">
@@ -4625,9 +4681,10 @@
       <c r="B123" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C123" s="10" t="s">
+      <c r="C123" t="s">
         <v>396</v>
       </c>
+      <c r="D123" s="19"/>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2" t="s">
@@ -4636,61 +4693,58 @@
       <c r="B124" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C124" s="10"/>
+      <c r="C124" s="5" t="s">
+        <v>399</v>
+      </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="C125" s="10"/>
+        <v>401</v>
+      </c>
+      <c r="C125" s="5"/>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C126" s="10"/>
+        <v>403</v>
+      </c>
+      <c r="C126" s="5"/>
     </row>
     <row r="127" spans="1:4">
-      <c r="A127" s="3" t="s">
-        <v>403</v>
+      <c r="A127" s="2" t="s">
+        <v>404</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C127" s="5"/>
     </row>
     <row r="128" spans="1:4">
-      <c r="A128" s="2" t="s">
-        <v>405</v>
+      <c r="A128" s="3" t="s">
+        <v>406</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="C128" t="s">
         <v>407</v>
       </c>
-      <c r="D128" s="2" t="s">
-        <v>408</v>
-      </c>
+      <c r="C128" s="5"/>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B129" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="C129" t="s">
         <v>410</v>
       </c>
-      <c r="C129" t="s">
+      <c r="D129" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4704,13 +4758,98 @@
         <v>414</v>
       </c>
       <c r="D130" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="2" t="s">
         <v>415</v>
       </c>
+      <c r="B131" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C131" t="s">
+        <v>417</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B132" s="20" t="s">
+        <v>420</v>
+      </c>
+      <c r="C132" s="21" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B133" s="22"/>
+      <c r="C133" s="21"/>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B134" s="22"/>
+      <c r="C134" s="21"/>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B135" s="22"/>
+      <c r="C135" s="21"/>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B136" s="22"/>
+      <c r="C136" s="21"/>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B137" s="22"/>
+      <c r="C137" s="21"/>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B138" s="22"/>
+      <c r="C138" s="21"/>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B139" s="22"/>
+      <c r="C139" s="21"/>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B140" s="22"/>
+      <c r="C140" s="21"/>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="C141" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="B132:B140"/>
     <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C123:C126"/>
+    <mergeCell ref="C132:C141"/>
     <mergeCell ref="D4:D7"/>
     <mergeCell ref="D20:D22"/>
     <mergeCell ref="D63:D93"/>

--- a/docs/game/items-zh_CN.xlsx
+++ b/docs/game/items-zh_CN.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="438">
   <si>
     <t>物品名称</t>
   </si>
@@ -634,14 +634,23 @@
     <t>其他树</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>一棵树。</t>
+    <t>/一棵枝干粗壮的树。看起来很靠谱。/一棵苹果树，偶尔会砸入你的生活。/一棵叶片苍翠的树，可能更有利于光合作用/一棵枝繁叶茂的树，可以供人乘凉。/一棵会开花的树。很美……/一棵长得很高的树。它未来会长到多高呢?</t>
+  </si>
+  <si>
+    <t>画笔</t>
+  </si>
+  <si>
+    <t>一种神奇的工具，能在画纸上留下你心灵的印记。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>…你尝试帮画技不过关的画师修改物品贴图…但什么都没有发生。/你决定不再去管画面里的一些瑕疵。</t>
     </r>
     <r>
       <rPr>
@@ -659,7 +668,222 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>一棵树。</t>
+      <t>你在这张桌子（这面墙）上留下了你的记忆。</t>
+    </r>
+  </si>
+  <si>
+    <t>画纸</t>
+  </si>
+  <si>
+    <t>一张白纸，貌似在等待着你的创作。</t>
+  </si>
+  <si>
+    <t>空白的画纸不意味着虚无，而意味着无限可能。</t>
+  </si>
+  <si>
+    <t>（进入绘画模式）</t>
+  </si>
+  <si>
+    <t>颜料</t>
+  </si>
+  <si>
+    <t>绘画用的颜料</t>
+  </si>
+  <si>
+    <t>五彩缤纷的颜料，正是对这个世界中美好事物的最好诠释</t>
+  </si>
+  <si>
+    <t>请不要把颜料挤得到处都是……虽然这可能会让本水塘更加“丰富多彩”？</t>
+  </si>
+  <si>
+    <t>画</t>
+  </si>
+  <si>
+    <t>你的作品。</t>
+  </si>
+  <si>
+    <t>画作往往是人们的心灵世界在真实世界的投影。这张画就是你对世界最好的表达。</t>
+  </si>
+  <si>
+    <t>（欣赏画作）</t>
+  </si>
+  <si>
+    <t>贝壳</t>
+  </si>
+  <si>
+    <t>自然的绚丽造物。同时也是本水塘的通用货币。</t>
+  </si>
+  <si>
+    <t>雨伞</t>
+  </si>
+  <si>
+    <t>异常气象的小调节器。能为你挡住阳光的曝晒和暴雨的侵袭</t>
+  </si>
+  <si>
+    <t>愿所有人都能在风雨之下获得片刻的安心。</t>
+  </si>
+  <si>
+    <t>（开合伞）</t>
+  </si>
+  <si>
+    <t>茶具套装</t>
+  </si>
+  <si>
+    <t>塘前观山景，帐内品茶香。</t>
+  </si>
+  <si>
+    <t>闲暇时光中，不如品一品茶。要开始沏茶吗？</t>
+  </si>
+  <si>
+    <t>船</t>
+  </si>
+  <si>
+    <t>能帮助你探索远方的工具。</t>
+  </si>
+  <si>
+    <t>（乘船）</t>
+  </si>
+  <si>
+    <t>黄瓜</t>
+  </si>
+  <si>
+    <t>一种喜欢攀爬在架子上的绿色蔬菜，能为你的生活增添一丝清凉。</t>
+  </si>
+  <si>
+    <t>生活往往需要一丝清新，来冲淡燥热与纷繁。</t>
+  </si>
+  <si>
+    <t>你吃掉了黄瓜，舌尖感受到了一阵（股）清爽。（清凉的气息涌入你的身体，你充满了冷静的力量。）(提示：食物类在使用前要提醒是否要吃掉。某些食物要提醒“不建议生吃掉掉”或“你会感觉很糟糕。”)</t>
+  </si>
+  <si>
+    <t>番茄</t>
+  </si>
+  <si>
+    <t>一种通红的蔬菜，酸酸甜甜，十分爽口。</t>
+  </si>
+  <si>
+    <t>通红似火的热情是无法深藏在内心的。</t>
+  </si>
+  <si>
+    <t>你吃掉了番茄。一种微微的甜丝丝的感觉渐渐在你舌尖化开，（一种奇妙的甜丝丝的感觉滑进了你的心头。）</t>
+  </si>
+  <si>
+    <t>土豆</t>
+  </si>
+  <si>
+    <t>一种万能的蔬菜，几乎怎么做都好吃。</t>
+  </si>
+  <si>
+    <t>无论土豆如何变化，不变的只有一颗热忱的心。</t>
+  </si>
+  <si>
+    <t>你吃掉了土豆。。。好吧，没什么味道。</t>
+  </si>
+  <si>
+    <t>蘑菇</t>
+  </si>
+  <si>
+    <t>一种隐匿在森林角落里的菌类，有一股别样的香气</t>
+  </si>
+  <si>
+    <t>嘭！</t>
+  </si>
+  <si>
+    <t>你吃掉了蘑菇。。。很奇怪的感觉，让你难以下咽。</t>
+  </si>
+  <si>
+    <t>白菜</t>
+  </si>
+  <si>
+    <t>最普通但最纯粹的蔬菜。能为菜品添加一些清新感</t>
+  </si>
+  <si>
+    <t>白菜貌似并不在乎当主角，它会在每道菜中都扮演好自己的角色，</t>
+  </si>
+  <si>
+    <t>你吃掉了白菜。。。很有嚼劲，但你的身体产生了某些奇妙的反应……</t>
+  </si>
+  <si>
+    <t>胡萝卜</t>
+  </si>
+  <si>
+    <t>一种躲在地底的蔬菜，口感比较脆爽。</t>
+  </si>
+  <si>
+    <t>胡萝卜貌似从来不显示它的浪漫，它只是一味向下扎根，然后捧起一片青绿。</t>
+  </si>
+  <si>
+    <t>你吃掉了胡萝卜。有种脆生生的感觉。（你的内心一阵愉悦。）（伴随着嚼胡萝卜的清脆声音，你的压力瞬间被驱散了。）</t>
+  </si>
+  <si>
+    <t>茄子</t>
+  </si>
+  <si>
+    <t>一种外表紫黑的蔬菜，但内心仍然青涩。</t>
+  </si>
+  <si>
+    <t>或许茄子也有成为一名蒙面侠客的梦想。</t>
+  </si>
+  <si>
+    <t>你吃掉了茄子。。。像是将一块海绵放进了嘴里。</t>
+  </si>
+  <si>
+    <t>水稻</t>
+  </si>
+  <si>
+    <t>一种常见的农作物，加工后可制成米饭。</t>
+  </si>
+  <si>
+    <t>一粒粒水稻种子能生长成一串串稻穗，新长出的稻粒又能作为种子孕育新的水稻。稻粒中或许凝结了某些生命的魔法吧。</t>
+  </si>
+  <si>
+    <t>苹果</t>
+  </si>
+  <si>
+    <t>一种常见的水果。</t>
+  </si>
+  <si>
+    <t>生活往往会不经意间给你惊喜。当然，苹果也会。</t>
+  </si>
+  <si>
+    <t>你吃掉了苹果。一股脆生生甜滋滋的感受爬上了你的舌尖。/伴随着清脆与甜润的交织，你有一股奇妙的感受。</t>
+  </si>
+  <si>
+    <t>西瓜</t>
+  </si>
+  <si>
+    <t>一种巨大的水果，是夏天最受欢迎的明星。</t>
+  </si>
+  <si>
+    <t>夏天最爽的事莫过于吹空调吃西瓜了。</t>
+  </si>
+  <si>
+    <t>你吃掉了西瓜。凉爽与甜蜜的感觉顿时涌来。/一阵阵凉爽而甜蜜的感觉攻占了你的神经，心头的燥热顿时烟消云散。</t>
+  </si>
+  <si>
+    <t>草莓</t>
+  </si>
+  <si>
+    <t>一种小小的水果，甜美可口</t>
+  </si>
+  <si>
+    <t>草莓很小，但最真实的热情，往往藏在一份份小小的甜蜜里。</t>
+  </si>
+  <si>
+    <t>你吃掉了草莓。一股浓烈的香甜在你舌尖摇曳（回荡，顿使你充满了活力）。（像是积淀了无数个日夜的甜味一瞬间在你舌尖炸开，顿使你充满了活力。）</t>
+  </si>
+  <si>
+    <t>橙子</t>
+  </si>
+  <si>
+    <t>一种酸甜多汁的水果。</t>
+  </si>
+  <si>
+    <t>保持对生活的赤“橙”之心（"corange"），才能酿出生活的甜。</t>
+  </si>
+  <si>
+    <r>
+      <t>你吃掉了橙子。酸甜的汁水从饱满的果粒中炸开，涌进嘴里。</t>
     </r>
     <r>
       <rPr>
@@ -677,7 +901,27 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>还是一棵树。</t>
+      <t>为口腔中带来一阵酸甜的冲击。</t>
+    </r>
+  </si>
+  <si>
+    <t>面粉</t>
+  </si>
+  <si>
+    <t>由小麦加工制成的食材，能够制作出多种多样的面食。</t>
+  </si>
+  <si>
+    <t>面团也许是厨房之中最普通的一员，但总会有一些厨师，用自己的巧手，将面团塑成千千万万种形态。创意会时不时地为你的生活带来一丝惊喜。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你把面粉弄到自己脸上了，哈哈！</t>
     </r>
     <r>
       <rPr>
@@ -695,7 +939,117 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>貌似是和其他树一样的一棵树。</t>
+      <t>你把面粉弄得到处都是……整个世界成了白色的海洋。</t>
+    </r>
+  </si>
+  <si>
+    <t>大米</t>
+  </si>
+  <si>
+    <t>水稻经加工之后的产物。</t>
+  </si>
+  <si>
+    <t>大米没有什么复杂的思想。或许它最大的梦想就是让人吃饱吧。</t>
+  </si>
+  <si>
+    <t>肉类</t>
+  </si>
+  <si>
+    <t>一种富有能量的食材。能极大地增添菜肴的吸引力。</t>
+  </si>
+  <si>
+    <t>以“饱”满的姿态面对生活！</t>
+  </si>
+  <si>
+    <t>你吃掉了生肉。。。这种口感实在令你难以下咽，但你强忍着吃掉完了。/你吃掉了生肉。。。你开始眼花缭乱，整个世界开始天旋地转。/你吃掉了生肉… …你晕过去了。</t>
+  </si>
+  <si>
+    <t>鸡蛋</t>
+  </si>
+  <si>
+    <t>一种美味的食物，富含蛋白质。</t>
+  </si>
+  <si>
+    <t>“这些鸡蛋能孵出小鸡吗？（・◇・)”</t>
+  </si>
+  <si>
+    <t>你剥开鸡蛋的外壳。鸡蛋液撒了一地。。。</t>
+  </si>
+  <si>
+    <t>盐</t>
+  </si>
+  <si>
+    <t>不可或缺的调味料。</t>
+  </si>
+  <si>
+    <t>吃饭是人类的生理需求，而“滋味”是人类享受美食的高阶追求。</t>
+  </si>
+  <si>
+    <t>糖</t>
+  </si>
+  <si>
+    <t>甜甜的调味料。在某些场景能起到画龙点睛的作用。</t>
+  </si>
+  <si>
+    <t>不如向生活里加点糖。</t>
+  </si>
+  <si>
+    <t>胡椒粉</t>
+  </si>
+  <si>
+    <t>比较辛辣的调味料。放在汤里有奇效。</t>
+  </si>
+  <si>
+    <t>啊嚏~</t>
+  </si>
+  <si>
+    <t>葱</t>
+  </si>
+  <si>
+    <t>一种作为调味品的蔬菜。</t>
+  </si>
+  <si>
+    <t>黄州狭港半江空，白饭青葱酒一钟。——袁说友</t>
+  </si>
+  <si>
+    <t>油</t>
+  </si>
+  <si>
+    <t>煎炒烹炸中不可或缺的食材。</t>
+  </si>
+  <si>
+    <t>如果将做饭比作音乐会，那么油便是摇滚乐队中的架子鼓手。菜品没有了油，便没有了激情。</t>
+  </si>
+  <si>
+    <t>黄油</t>
+  </si>
+  <si>
+    <t>总是活跃在甜点制作的舞台，</t>
+  </si>
+  <si>
+    <t>如果生活是块干面包，那么，何不尝试为生活烙上金黄与奶香？</t>
+  </si>
+  <si>
+    <t>烤鱼</t>
+  </si>
+  <si>
+    <t>美味的烤鱼。依旧能感到营火的温暖（鱼肉的鲜味被营火完美地激发）。</t>
+  </si>
+  <si>
+    <t>没有什么是吃顿烤鱼解决不了的，如果有就两顿。</t>
+  </si>
+  <si>
+    <t>鱼汤</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>鲜美的鱼汤。仿佛能闻到独特的清鲜</t>
     </r>
     <r>
       <rPr>
@@ -713,24 +1067,123 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>…你打量着这些树。貌似它们都只是一棵棵单调的树。……但又貌似并不是。……/你仔细看去。每一棵树、每一片叶子貌似都有自己的故事。……这并不是一棵棵单调的树，而是一棵棵独特的树。/一棵枝干粗壮的树。/一棵果实硕大的树。/一棵叶片苍翠的树。/一棵枝繁叶茂的树。/一棵会开花的树。（孩子们，这版好像有点太刻意了。我还有planB，直接把艾青诗选写上。）</t>
-    </r>
-  </si>
-  <si>
-    <t>画笔</t>
-  </si>
-  <si>
-    <t>一种神奇的工具，能在画纸上留下你心灵的印记。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>…你尝试帮画技不过关的画师修改物品贴图…但什么都没有发生。/你决定不再去管画面里的一些瑕疵。</t>
+      <t>充盈着自然的纯粹。</t>
+    </r>
+  </si>
+  <si>
+    <t>平平无奇的水，经过长时间的熬煮、各种食材的激发、以及你的烹饪，也能产生魔法。</t>
+  </si>
+  <si>
+    <t>清蒸鱼</t>
+  </si>
+  <si>
+    <t>质朴但美味的做法（虽平淡但回味无穷。）</t>
+  </si>
+  <si>
+    <t>最纯真的味道无需修饰。</t>
+  </si>
+  <si>
+    <t>烤肉</t>
+  </si>
+  <si>
+    <t>美味的烤肉。依旧能感到营火的温暖（肉的鲜香被营火生动地展现/附带着营火特殊的烟熏气味）</t>
+  </si>
+  <si>
+    <t>烧烤的魅力，往往就在于它纯真朴实的烟火气。</t>
+  </si>
+  <si>
+    <t>炸鱼/炸肉</t>
+  </si>
+  <si>
+    <t>酥脆与嫩滑兼具的食物（完美结合的产物），（一口中有无穷的体验）。</t>
+  </si>
+  <si>
+    <t>至少我还有炸肉/炸鱼。</t>
+  </si>
+  <si>
+    <t>番茄炒蛋</t>
+  </si>
+  <si>
+    <t>最普通的家常菜之一。（即使是普通的家常菜，在你的手下也有别样的美味。）</t>
+  </si>
+  <si>
+    <t>总有人争吵番茄炒蛋的口味。其实，她是一位可甜可盐的阳光女孩哦！！</t>
+  </si>
+  <si>
+    <t>蘑菇炒肉</t>
+  </si>
+  <si>
+    <t>相得益彰的搭配！（鲜美的肉片附带着蘑菇的清香。）</t>
+  </si>
+  <si>
+    <t>单调的味道无法造就美味的菜品，肉与蘑菇的互补正是对于烹饪的启示。</t>
+  </si>
+  <si>
+    <t>西红柿拌白糖</t>
+  </si>
+  <si>
+    <t>一道甜丝丝的凉菜/一盘甜蜜的清梦。</t>
+  </si>
+  <si>
+    <t>火山飘雪？</t>
+  </si>
+  <si>
+    <t>番茄炒黄瓜</t>
+  </si>
+  <si>
+    <t>眼前一亮的菜品/小清新风格的菜品。</t>
+  </si>
+  <si>
+    <t>红配绿</t>
+  </si>
+  <si>
+    <t>清炒时蔬</t>
+  </si>
+  <si>
+    <t>健康而有活力/生机勃勃、活力满满的菜品。</t>
+  </si>
+  <si>
+    <t>就让新鲜的蔬菜带给你活力。</t>
+  </si>
+  <si>
+    <t>炖菜（统）</t>
+  </si>
+  <si>
+    <t>（）与（）交织，汤汁渗到食物里，产生了奇妙的反应。（闻起来很好，但貌似有点煮烂了/硬？）</t>
+  </si>
+  <si>
+    <t>耐心的等待，美味总会融于一炉。</t>
+  </si>
+  <si>
+    <t>包子</t>
+  </si>
+  <si>
+    <t>（）馅的包子。看起来不错。/外表雪白，皮薄馅大。</t>
+  </si>
+  <si>
+    <t>外表不是判断一个包子味道的标准，内心才是。</t>
+  </si>
+  <si>
+    <t>饺子</t>
+  </si>
+  <si>
+    <t>（）馅的饺子。看起来很不错。/似有一股别样的温暖洋溢。</t>
+  </si>
+  <si>
+    <t>饺子绝对是最有人情味的食物，它见证过一场又一场团圆，书写着一段又一段不同而又相同的爱的故事。</t>
+  </si>
+  <si>
+    <t>面条</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一种热气腾腾的食物，（隐隐散发出</t>
     </r>
     <r>
       <rPr>
@@ -748,228 +1201,42 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>你在这张桌子（这面墙）上留下了你的记忆。</t>
-    </r>
-  </si>
-  <si>
-    <t>画纸</t>
-  </si>
-  <si>
-    <t>一张白纸，貌似在等待着你的创作。</t>
-  </si>
-  <si>
-    <t>空白的画纸不意味着虚无，而意味着无限可能。</t>
-  </si>
-  <si>
-    <t>（进入绘画模式）</t>
-  </si>
-  <si>
-    <t>颜料</t>
-  </si>
-  <si>
-    <t>绘画用的颜料</t>
-  </si>
-  <si>
-    <t>五彩缤纷的颜料，正是对这个世界中美好事物的最好诠释</t>
-  </si>
-  <si>
-    <t>请不要把颜料挤得到处都是……虽然这可能会让本水塘更加“丰富多彩”？</t>
-  </si>
-  <si>
-    <t>画</t>
-  </si>
-  <si>
-    <t>你的作品。</t>
-  </si>
-  <si>
-    <t>画作往往是人们的心灵世界在真实世界的投影。这张画就是你对世界最好的表达。</t>
-  </si>
-  <si>
-    <t>（欣赏画作）</t>
-  </si>
-  <si>
-    <t>贝壳</t>
-  </si>
-  <si>
-    <t>自然的绚丽造物。同时也是本水塘的通用货币。</t>
-  </si>
-  <si>
-    <t>雨伞</t>
-  </si>
-  <si>
-    <t>异常气象的小调节器。能为你挡住阳光的曝晒和暴雨的侵袭</t>
-  </si>
-  <si>
-    <t>愿所有人都能在风雨之下获得片刻的安心。</t>
-  </si>
-  <si>
-    <t>（开合伞）</t>
-  </si>
-  <si>
-    <t>茶具套装</t>
-  </si>
-  <si>
-    <t>塘前观山景，帐内品茶香。</t>
-  </si>
-  <si>
-    <t>闲暇时光中，不如品一品茶。要开始沏茶吗？</t>
-  </si>
-  <si>
-    <t>船</t>
-  </si>
-  <si>
-    <t>能帮助你探索远方的工具。</t>
-  </si>
-  <si>
-    <t>（乘船）</t>
-  </si>
-  <si>
-    <t>黄瓜</t>
-  </si>
-  <si>
-    <t>一种喜欢攀爬在架子上的绿色蔬菜，能为你的生活增添一丝清凉。</t>
-  </si>
-  <si>
-    <t>生活往往需要一丝清新，来冲淡燥热与纷繁。</t>
-  </si>
-  <si>
-    <t>你吃掉了黄瓜，舌尖感受到了一阵（股）清爽。（清凉的气息涌入你的身体，你充满了冷静的力量。）(提示：食物类在使用前要提醒是否要吃掉。某些食物要提醒“不建议生吃掉掉”或“你会感觉很糟糕。”)</t>
-  </si>
-  <si>
-    <t>番茄</t>
-  </si>
-  <si>
-    <t>一种通红的蔬菜，酸酸甜甜，十分爽口。</t>
-  </si>
-  <si>
-    <t>通红似火的热情是无法深藏在内心的。</t>
-  </si>
-  <si>
-    <t>你吃掉了番茄。一种微微的甜丝丝的感觉渐渐在你舌尖化开，（一种奇妙的甜丝丝的感觉滑进了你的心头。）</t>
-  </si>
-  <si>
-    <t>土豆</t>
-  </si>
-  <si>
-    <t>一种万能的蔬菜，几乎怎么做都好吃。</t>
-  </si>
-  <si>
-    <t>无论土豆如何变化，不变的只有一颗热忱的心。</t>
-  </si>
-  <si>
-    <t>你吃掉了土豆。。。好吧，没什么味道。</t>
-  </si>
-  <si>
-    <t>蘑菇</t>
-  </si>
-  <si>
-    <t>一种隐匿在森林角落里的菌类，有一股别样的香气</t>
-  </si>
-  <si>
-    <t>嘭！</t>
-  </si>
-  <si>
-    <t>你吃掉了蘑菇。。。很奇怪的感觉，让你难以下咽。</t>
-  </si>
-  <si>
-    <t>白菜</t>
-  </si>
-  <si>
-    <t>最普通但最纯粹的蔬菜。能为菜品添加一些清新感</t>
-  </si>
-  <si>
-    <t>白菜貌似并不在乎当主角，它会在每道菜中都扮演好自己的角色，</t>
-  </si>
-  <si>
-    <t>你吃掉了白菜。。。很有嚼劲，但你的身体产生了某些奇妙的反应……</t>
-  </si>
-  <si>
-    <t>胡萝卜</t>
-  </si>
-  <si>
-    <t>一种躲在地底的蔬菜，口感比较脆爽。</t>
-  </si>
-  <si>
-    <t>胡萝卜貌似从来不显示它的浪漫，它只是一味向下扎根，然后捧起一片青绿。</t>
-  </si>
-  <si>
-    <t>你吃掉了胡萝卜。有种脆生生的感觉。（你的内心一阵愉悦。）（伴随着嚼胡萝卜的清脆声音，你的压力瞬间被驱散了。）</t>
-  </si>
-  <si>
-    <t>茄子</t>
-  </si>
-  <si>
-    <t>一种外表紫黑的蔬菜，但内心仍然青涩。</t>
-  </si>
-  <si>
-    <t>或许茄子也有成为一名蒙面侠客的梦想。</t>
-  </si>
-  <si>
-    <t>你吃掉了茄子。。。像是将一块海绵放进了嘴里。</t>
-  </si>
-  <si>
-    <t>水稻</t>
-  </si>
-  <si>
-    <t>一种常见的农作物，加工后可制成米饭。</t>
-  </si>
-  <si>
-    <t>一粒粒水稻种子能生长成一串串稻穗，新长出的稻粒又能作为种子孕育新的水稻。稻粒中或许凝结了某些生命的魔法吧。</t>
-  </si>
-  <si>
-    <t>苹果</t>
-  </si>
-  <si>
-    <t>一种常见的水果。</t>
-  </si>
-  <si>
-    <t>生活往往会不经意间给你惊喜。当然，苹果也会。</t>
-  </si>
-  <si>
-    <t>你吃掉了苹果。一股脆生生甜滋滋的感受爬上了你的舌尖。/伴随着清脆与甜润的交织，你有一股奇妙的感受。</t>
-  </si>
-  <si>
-    <t>西瓜</t>
-  </si>
-  <si>
-    <t>一种巨大的水果，是夏天最受欢迎的明星。</t>
-  </si>
-  <si>
-    <t>夏天最爽的事莫过于吹空调吃西瓜了。</t>
-  </si>
-  <si>
-    <t>你吃掉了西瓜。凉爽与甜蜜的感觉顿时涌来。/一阵阵凉爽而甜蜜的感觉攻占了你的神经，心头的燥热顿时烟消云散。</t>
-  </si>
-  <si>
-    <t>草莓</t>
-  </si>
-  <si>
-    <t>一种小小的水果，酸甜可口</t>
-  </si>
-  <si>
-    <t>草莓很小，但最真实的热情，往往藏在一份份小小的甜蜜里。</t>
-  </si>
-  <si>
-    <t>你吃掉了草莓。一股浓烈的香甜在你舌尖摇曳（回荡，顿使你充满了活力）。（像是积淀了无数个日夜的甜味一瞬间在你舌尖炸开，顿使你充满了活力。）</t>
-  </si>
-  <si>
-    <t>面粉</t>
-  </si>
-  <si>
-    <t>由小麦加工制成的食材，能够制作出多种多样的面食。</t>
-  </si>
-  <si>
-    <t>面团也许是厨房之中最普通的一员，但总会有一些厨师，用自己的巧手，将面团塑成千千万万种形态。创意会时不时地为你的生活带来一丝惊喜。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你把面粉弄到自己脸上了，哈哈！</t>
+      <t>充斥着驱散疲惫的魔力。）</t>
+    </r>
+  </si>
+  <si>
+    <t>无论发生什么，一碗热面往往会带来暖心的慰藉。</t>
+  </si>
+  <si>
+    <t>苹果烧肉（隐）</t>
+  </si>
+  <si>
+    <t>酸甜可口的烧肉。（苹果的汁水为其注入了灵魂。）</t>
+  </si>
+  <si>
+    <t>没想到普普通通的水果，换了一个赛道之后便能焕发出别样的光彩。</t>
+  </si>
+  <si>
+    <t>炒菜（统）</t>
+  </si>
+  <si>
+    <t>普通的炒菜。/即使是普通的炒菜，也有独特的光彩</t>
+  </si>
+  <si>
+    <t>你真的“炒”级棒哦!（^▽^）!</t>
+  </si>
+  <si>
+    <t>煎鸡蛋</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>焦黄（鲜嫩）的煎蛋。火候适宜</t>
     </r>
     <r>
       <rPr>
@@ -987,120 +1254,39 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>你把面粉弄得到处都是……整个世界成了白色的海洋。</t>
-    </r>
-  </si>
-  <si>
-    <t>大米</t>
-  </si>
-  <si>
-    <t>水稻经加工之后的产物。</t>
-  </si>
-  <si>
-    <t>大米没有什么复杂的思想。或许它最大的梦想就是让人吃饱吧。</t>
-  </si>
-  <si>
-    <t>肉类</t>
-  </si>
-  <si>
-    <t>一种富有能量的食材。能极大地增添菜肴的吸引力。</t>
-  </si>
-  <si>
-    <t>以“饱”满的姿态面对生活！</t>
-  </si>
-  <si>
-    <t>你吃掉了生肉。。。这种口感实在令你难以下咽，但你强忍着吃掉完了。/你吃掉了生肉。。。你开始眼花缭乱，整个世界开始天旋地转。/你吃掉了生肉… …你晕过去了。</t>
-  </si>
-  <si>
-    <t>鸡蛋</t>
-  </si>
-  <si>
-    <t>一种美味的食物，富含蛋白质。</t>
-  </si>
-  <si>
-    <t>“这些鸡蛋能孵出小鸡吗？（・◇・)”</t>
-  </si>
-  <si>
-    <t>你剥开鸡蛋的外壳。鸡蛋液撒了一地。。。</t>
-  </si>
-  <si>
-    <t>盐</t>
-  </si>
-  <si>
-    <t>不可或缺的调味料。</t>
-  </si>
-  <si>
-    <t>吃饭是人类的生理需求，而“滋味”是人类享受美食的高阶追求。</t>
-  </si>
-  <si>
-    <t>糖</t>
-  </si>
-  <si>
-    <t>甜甜的调味料。在某些场景能起到画龙点睛的作用。</t>
-  </si>
-  <si>
-    <t>不如向生活里加点糖。</t>
-  </si>
-  <si>
-    <t>胡椒粉</t>
-  </si>
-  <si>
-    <t>比较辛辣的调味料。放在汤里有奇效。</t>
-  </si>
-  <si>
-    <t>啊嚏~</t>
-  </si>
-  <si>
-    <t>葱</t>
-  </si>
-  <si>
-    <t>一种作为调味品的蔬菜。</t>
-  </si>
-  <si>
-    <t>黄州狭港半江空，白饭青葱酒一钟。——袁说友</t>
-  </si>
-  <si>
-    <t>油</t>
-  </si>
-  <si>
-    <t>煎炒烹炸中不可或缺的食材。</t>
-  </si>
-  <si>
-    <t>如果将做饭比作音乐会，那么油便是摇滚乐队中的架子鼓手。菜品没有了油，便没有了激情。</t>
-  </si>
-  <si>
-    <t>黄油</t>
-  </si>
-  <si>
-    <t>总是活跃在甜点制作的舞台，</t>
-  </si>
-  <si>
-    <t>如果生活是块干面包，那么，何不尝试为生活烙上金黄与奶香？</t>
-  </si>
-  <si>
-    <t>烤鱼</t>
-  </si>
-  <si>
-    <t>美味的烤鱼。依旧能感到营火的温暖（鱼肉的鲜味被营火完美地激发）。</t>
-  </si>
-  <si>
-    <t>没有什么是吃顿烤鱼解决不了的，如果有就两顿。</t>
-  </si>
-  <si>
-    <t>另附文件</t>
-  </si>
-  <si>
-    <t>鱼汤</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>鲜美的鱼汤。仿佛能闻到独特的清鲜</t>
+      <t>金黄的煎蛋。露出了欢快的笑脸。/溏心蛋。貌似还没熟，不过有种别样的口感。</t>
+    </r>
+  </si>
+  <si>
+    <t>当你的生活开始下雨，不妨煎个鸡蛋。这样碗里就会出现一个小太阳。</t>
+  </si>
+  <si>
+    <t>煮鸡蛋</t>
+  </si>
+  <si>
+    <t>水煮后的鸡蛋，剥开壳品尝吧！</t>
+  </si>
+  <si>
+    <t>看似冷冰冰的外壳之下，隐藏的是一颗金黄炽热的心</t>
+  </si>
+  <si>
+    <t>土豆炖肉</t>
+  </si>
+  <si>
+    <t>经典款的炖菜。肉的香气充分/完美与土豆结合，令人食欲大增！</t>
+  </si>
+  <si>
+    <t>烧茄子</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>色香味俱全的完美造物！</t>
     </r>
     <r>
       <rPr>
@@ -1118,123 +1304,33 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>充盈着自然的纯粹。</t>
-    </r>
-  </si>
-  <si>
-    <t>平平无奇的水，经过长时间的熬煮、各种食材的激发、以及你的烹饪，也能产生魔法。</t>
-  </si>
-  <si>
-    <t>清蒸鱼</t>
-  </si>
-  <si>
-    <t>质朴但美味的做法（虽平淡但回味无穷。）</t>
-  </si>
-  <si>
-    <t>最纯真的味道无需修饰。</t>
-  </si>
-  <si>
-    <t>烤肉</t>
-  </si>
-  <si>
-    <t>美味的烤肉。依旧能感到营火的温暖（肉的鲜香被营火生动地展现/附带着营火特殊的烟熏气味）</t>
-  </si>
-  <si>
-    <t>烧烤的魅力，往往就在于它纯真朴实的烟火气。</t>
-  </si>
-  <si>
-    <t>炸鱼/炸肉</t>
-  </si>
-  <si>
-    <t>酥脆与嫩滑兼具的食物（完美结合的产物），（一口中有无穷的体验）。</t>
-  </si>
-  <si>
-    <t>至少我还有炸肉/炸鱼。</t>
-  </si>
-  <si>
-    <t>番茄炒蛋</t>
-  </si>
-  <si>
-    <t>最普通的家常菜之一。（即使是普通的家常菜，在你的手下也有别样的美味。）</t>
-  </si>
-  <si>
-    <t>总有人争吵番茄炒蛋的口味。其实，她是一位可甜可盐的阳光女孩哦！！</t>
-  </si>
-  <si>
-    <t>蘑菇炒肉</t>
-  </si>
-  <si>
-    <t>相得益彰的搭配！（鲜美的肉片附带着蘑菇的清香。）</t>
-  </si>
-  <si>
-    <t>单调的味道无法造就美味的菜品，肉与蘑菇的互补正是对于烹饪的启示。</t>
-  </si>
-  <si>
-    <t>西红柿拌白糖</t>
-  </si>
-  <si>
-    <t>一道甜丝丝的凉菜/一盘甜蜜的清梦。</t>
-  </si>
-  <si>
-    <t>火山飘雪？</t>
-  </si>
-  <si>
-    <t>番茄炒黄瓜</t>
-  </si>
-  <si>
-    <t>眼前一亮的菜品/小清新风格的菜品。</t>
-  </si>
-  <si>
-    <t>红配绿</t>
-  </si>
-  <si>
-    <t>清炒时蔬</t>
-  </si>
-  <si>
-    <t>健康而有活力/生机勃勃、活力满满的菜品。</t>
-  </si>
-  <si>
-    <t>就让新鲜的蔬菜带给你活力。</t>
-  </si>
-  <si>
-    <t>炖菜（统）</t>
-  </si>
-  <si>
-    <t>（）与（）交织，汤汁渗到食物里，产生了奇妙的反应。（闻起来很好，但貌似有点煮烂了/硬？）</t>
-  </si>
-  <si>
-    <t>耐心的等待，美味总会融于一炉。</t>
-  </si>
-  <si>
-    <t>包子</t>
-  </si>
-  <si>
-    <t>（）馅的包子。看起来不错。/外表雪白，皮薄馅大。</t>
-  </si>
-  <si>
-    <t>外表不是判断一个包子味道的标准，内心才是。</t>
-  </si>
-  <si>
-    <t>饺子</t>
-  </si>
-  <si>
-    <t>（）馅的饺子。看起来很不错。/似有一股别样的温暖洋溢。</t>
-  </si>
-  <si>
-    <t>饺子绝对是最有人情味的食物，它见证过一场又一场团圆，书写着一段又一段不同而又相同的爱的故事。</t>
-  </si>
-  <si>
-    <t>面条</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>一种热气腾腾的食物，（隐隐散发出</t>
+      <t>色香味俱全的家常菜。</t>
+    </r>
+  </si>
+  <si>
+    <t>茄子总喜欢把自己打扮得油亮油亮的。</t>
+  </si>
+  <si>
+    <t>蛋炒饭</t>
+  </si>
+  <si>
+    <t>普通的米饭在鸡蛋的衬托下显出美味/充满阳光</t>
+  </si>
+  <si>
+    <t>普通的米饭也有成为主角的梦</t>
+  </si>
+  <si>
+    <t>烤土豆</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>洋溢着金黄的烤土豆。火候恰到好处！</t>
     </r>
     <r>
       <rPr>
@@ -1252,42 +1348,155 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>充斥着驱散疲惫的魔力。）</t>
-    </r>
-  </si>
-  <si>
-    <t>无论发生什么，一碗热面往往会带来暖心的慰藉。</t>
-  </si>
-  <si>
-    <t>苹果烧肉（隐）</t>
-  </si>
-  <si>
-    <t>酸甜可口的烧肉。（苹果的汁水为其注入了灵魂。）</t>
-  </si>
-  <si>
-    <t>没想到普普通通的水果，换了一个赛道之后便能焕发出别样的光彩。</t>
-  </si>
-  <si>
-    <t>炒菜（统）</t>
-  </si>
-  <si>
-    <t>普通的炒菜。/即使是普通的炒菜，也有独特的光彩</t>
-  </si>
-  <si>
-    <t>你真的“炒”级棒哦!（^▽^）!</t>
-  </si>
-  <si>
-    <t>煎鸡蛋</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>焦黄（鲜嫩）的煎蛋。火候适宜</t>
+      <t>焦黄（软嫩）的烤土豆。</t>
+    </r>
+  </si>
+  <si>
+    <t>土豆总是沉默寡言，但它会将营地的温暖酿成金黄。</t>
+  </si>
+  <si>
+    <t>馒头</t>
+  </si>
+  <si>
+    <t>普通的面食，亦有乾坤。</t>
+  </si>
+  <si>
+    <t>中式无糖小面包？</t>
+  </si>
+  <si>
+    <t>你吃掉了馒头，一阵软绵绵的面团在舌尖膨起，放松了你的味蕾。</t>
+  </si>
+  <si>
+    <t>米饭</t>
+  </si>
+  <si>
+    <t>生活中不可或缺的主食</t>
+  </si>
+  <si>
+    <t>雪白如玉的米粒是水稻经过时间的积淀。</t>
+  </si>
+  <si>
+    <t>苹果派（隐）</t>
+  </si>
+  <si>
+    <t>一种温馨的甜点。（完美地）融入了苹果的香气。</t>
+  </si>
+  <si>
+    <t>氤氲苹果香，和暖透心肠。</t>
+  </si>
+  <si>
+    <t>蛋糕</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一种大号的甜品，松软醇甜（回味无穷）。/生日快乐|ू</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ω</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>` )</t>
+    </r>
+  </si>
+  <si>
+    <t>人们总会向蛋糕中注入热情与爱。这也是蛋糕甜的来源。</t>
+  </si>
+  <si>
+    <t>蘑菇炒饭（隐）</t>
+  </si>
+  <si>
+    <t>蕴含着蘑菇独特香气的炒饭。/将蘑菇的香气完美表现的炒饭</t>
+  </si>
+  <si>
+    <t>烤苹果（隐）</t>
+  </si>
+  <si>
+    <t>奇特的想法！但貌似缺少了一点什么。/奇特而美味的菜品！</t>
+  </si>
+  <si>
+    <t>偶尔的探索，也能有不错的收获。</t>
+  </si>
+  <si>
+    <t>汤（统）</t>
+  </si>
+  <si>
+    <t>鲜美的汤。（将（）的味道完美融入）</t>
+  </si>
+  <si>
+    <t>炸蘑菇</t>
+  </si>
+  <si>
+    <t>经过油炸之后变得脆脆（香脆可口）的蘑菇。</t>
+  </si>
+  <si>
+    <t>到底还有什么东西是不能炸的呢？</t>
+  </si>
+  <si>
+    <t>冷饮</t>
+  </si>
+  <si>
+    <t>夏日解暑神器！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">冰镇饮料，快乐“凉”多。 </t>
+  </si>
+  <si>
+    <t>炸小鱼</t>
+  </si>
+  <si>
+    <t>经油炸后金黄酥脆的小鱼，（焦香爽口，使味蕾激荡。）</t>
+  </si>
+  <si>
+    <t>有时厨房往往就是这么神奇，鱼只是体型不同，炸出来却完全是两种味道。</t>
+  </si>
+  <si>
+    <t>小鱼干</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小鱼经过加工之后的产物。</t>
     </r>
     <r>
       <rPr>
@@ -1296,6 +1505,68 @@
         <rFont val="HarmonyOS Sans SC"/>
         <charset val="134"/>
       </rPr>
+      <t>Cat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>貌似很感兴趣。</t>
+    </r>
+  </si>
+  <si>
+    <t>钓上来的小鱼一定要全部做成小鱼干，然后喂给Cat！——不是Cat</t>
+  </si>
+  <si>
+    <t>你吃掉了小鱼干，咸鲜的感觉伴随着牙尖的咀嚼，扩散到了口腔的每个角落。</t>
+  </si>
+  <si>
+    <t>冰激凌</t>
+  </si>
+  <si>
+    <t>夏天最受欢迎的食品。（温馨提示：冰激凌如果不直接吃的话，还有妙用！）</t>
+  </si>
+  <si>
+    <t>在炎炎夏日中，总有一些手段，能在你的心头保留一片冬天。</t>
+  </si>
+  <si>
+    <t>你吃掉了冰激凌。舌尖涌起一阵阵甜蜜与清凉，带走了燥热与烦恼。</t>
+  </si>
+  <si>
+    <t>果盘</t>
+  </si>
+  <si>
+    <t>各种水果摆在一起，产生了一种新的美食。</t>
+  </si>
+  <si>
+    <t>果盘的特色，便是不同水果的各具特色</t>
+  </si>
+  <si>
+    <t>你吃掉了果盘，各种水果的酸甜在口中此起彼伏/澎湃。</t>
+  </si>
+  <si>
+    <t>小蛋糕</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>简约版的蛋糕，但依旧美味。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="HarmonyOS Sans SC"/>
+        <charset val="134"/>
+      </rPr>
       <t>/</t>
     </r>
     <r>
@@ -1305,40 +1576,172 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>金黄的煎蛋。露出了欢快的笑脸。/溏心蛋。貌似还没熟，不过有种别样的口感。</t>
-    </r>
-  </si>
-  <si>
-    <t>当你的生活开始下雨，不妨煎个鸡蛋。这样碗里就会出现一个小太阳。</t>
-  </si>
-  <si>
-    <t>煮鸡蛋</t>
-  </si>
-  <si>
-    <t>水煮后的鸡蛋，剥开壳品尝吧！</t>
-  </si>
-  <si>
-    <t>看似冷冰冰的外壳之下，隐藏的是一颗金黄炽热的心</t>
-  </si>
-  <si>
-    <t>土豆炖肉</t>
-  </si>
-  <si>
-    <t>经典款的炖菜。肉的香气充分/完美与土豆结合，令人食欲大增！</t>
-  </si>
-  <si>
-    <t>烧茄子</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>色香味俱全的完美造物！</t>
-    </r>
+      <t>但同样松软醇甜。</t>
+    </r>
+  </si>
+  <si>
+    <t>小小的蛋糕，大大的温暖。</t>
+  </si>
+  <si>
+    <t>水煮肉片</t>
+  </si>
+  <si>
+    <t>在熬煮过程中变得鲜香可口（嫩滑爽口）的肉片</t>
+  </si>
+  <si>
+    <t>古语有云，水煮肉片，水加多者为肉片汤，水加少者为滑肉。</t>
+  </si>
+  <si>
+    <t>草鱼</t>
+  </si>
+  <si>
+    <t>一种河塘中常见的鱼，也是餐桌上的常客。</t>
+  </si>
+  <si>
+    <t>草鱼貌似是位素食的狂热者。这也是它名字的由来。</t>
+  </si>
+  <si>
+    <t>或许你觉得让它在塘中漫游，才是更好的选择。要放生它吗？</t>
+  </si>
+  <si>
+    <t>鲈鱼</t>
+  </si>
+  <si>
+    <t>一种背部生有黑斑的鱼，常用于清蒸。</t>
+  </si>
+  <si>
+    <t>此行不为鲈鱼鲙，自爱名山入剡中。——李白</t>
+  </si>
+  <si>
+    <t>鲤鱼</t>
+  </si>
+  <si>
+    <t>一种被认为象征幸运的鱼。</t>
+  </si>
+  <si>
+    <t>鲤鱼对自己能带来幸运一事，同样感到幸运。</t>
+  </si>
+  <si>
+    <t>鲫鱼</t>
+  </si>
+  <si>
+    <t>一种身体比较圆润的鱼，能在汤中激发鲜香的滋味。</t>
+  </si>
+  <si>
+    <t>鲫鱼总是在塘中默默游走，随波逐流，随遇而安。</t>
+  </si>
+  <si>
+    <t>鲅鱼</t>
+  </si>
+  <si>
+    <t>一种身体细长，布有蓝色斑点的鱼，可用于包饺子。</t>
+  </si>
+  <si>
+    <t>鲅鱼可是名副其实的旅行家，它的目标可不止一片小塘。</t>
+  </si>
+  <si>
+    <t>小黄鱼</t>
+  </si>
+  <si>
+    <t>一种小小的金黄色的鱼，适配各种烹饪方法。</t>
+  </si>
+  <si>
+    <t>小黄鱼往往身居水底，却把自己活成了金色的阳光。</t>
+  </si>
+  <si>
+    <t>石斑鱼</t>
+  </si>
+  <si>
+    <t>其貌不扬，味道却很突出。</t>
+  </si>
+  <si>
+    <t>不要小看石斑鱼的外貌。这也是它捕猎的手段之一。</t>
+  </si>
+  <si>
+    <t>鲳鱼</t>
+  </si>
+  <si>
+    <t>一种身体扁扁的大头鱼。</t>
+  </si>
+  <si>
+    <t>鲳鱼又在用它的大脑袋思考什么呢？</t>
+  </si>
+  <si>
+    <t>带鱼</t>
+  </si>
+  <si>
+    <t>一种身体很长的鱼，常用于红烧。</t>
+  </si>
+  <si>
+    <t>希望你每天笑脸“长”在。（There's no need to keep your face long.）</t>
+  </si>
+  <si>
+    <t>河豚</t>
+  </si>
+  <si>
+    <t>一种会变得圆滚滚的鱼。（温馨提示：非专业人士谨慎烹饪！）</t>
+  </si>
+  <si>
+    <t>美味的诱惑，有时也伴随着致命的风险。</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
+    <t>一种神奇的鱼，周身散发着微弱的幽蓝。</t>
+  </si>
+  <si>
+    <t>其他鱼类往往对青鱼总喜欢像幽灵一样，深居水塘内部感到奇怪。其实，它只是将自己的内心套上了一层保护色。</t>
+  </si>
+  <si>
+    <t>河虾</t>
+  </si>
+  <si>
+    <t>隐匿于浅塘中的节肢动物。</t>
+  </si>
+  <si>
+    <t>河虾总自认为是水塘中的神秘侠客。它们习惯隐藏自己，在夜晚才开始一天的生活。</t>
+  </si>
+  <si>
+    <t>鲦鱼</t>
+  </si>
+  <si>
+    <t>一种活泼敏捷的小鱼。</t>
+  </si>
+  <si>
+    <t>鲦鱼出游从容，是鱼之乐也。——《庄子》</t>
+  </si>
+  <si>
+    <t>水草</t>
+  </si>
+  <si>
+    <t>一种水生藻类植物，虽然营养价值极高，但经常被人们忽视。</t>
+  </si>
+  <si>
+    <t>水草不是垃圾，它在餐桌上的价值可不比鱼类差！</t>
+  </si>
+  <si>
+    <t>玻璃瓶</t>
+  </si>
+  <si>
+    <t>曾经装过信纸的玻璃瓶。或许可以用它干点什么有意思的事……</t>
+  </si>
+  <si>
+    <t>玻璃瓶很小，但却能大到容纳世间一切浪漫。</t>
+  </si>
+  <si>
+    <t>（装东西）</t>
+  </si>
+  <si>
+    <t>一朵花</t>
+  </si>
+  <si>
+    <t>曾经生长在大自然中的植物，现在正在玻璃瓶中静静绽放。</t>
+  </si>
+  <si>
+    <t>今天也要保持绽放哦！</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1346,6 +1749,62 @@
         <rFont val="HarmonyOS Sans SC"/>
         <charset val="134"/>
       </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可放置。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="HarmonyOS Sans SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你看到这朵花仍在绽放，心情舒畅了许多。</t>
+    </r>
+  </si>
+  <si>
+    <t>一瓶水</t>
+  </si>
+  <si>
+    <t>生命生长的必要物资。</t>
+  </si>
+  <si>
+    <t>生命的奇迹便源于这种普通的物质。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你喝掉了水。一股清凉透过你的心尖。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="HarmonyOS Sans SC"/>
+        <charset val="134"/>
+      </rPr>
       <t>/</t>
     </r>
     <r>
@@ -1355,33 +1814,54 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>色香味俱全的家常菜。</t>
-    </r>
-  </si>
-  <si>
-    <t>茄子总喜欢把自己打扮得油亮油亮的。</t>
-  </si>
-  <si>
-    <t>蛋炒饭</t>
-  </si>
-  <si>
-    <t>普通的米饭在鸡蛋的衬托下显出美味/充满阳光</t>
-  </si>
-  <si>
-    <t>普通的米饭也有成为主角的梦</t>
-  </si>
-  <si>
-    <t>烤土豆</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>洋溢着金黄的烤土豆。火候恰到好处！</t>
+      <t>你为农作物浇了水。。幼苗经过你的洗礼，生长得更旺盛了。但你或许应该用你的水壶。/…你为水塘补充了水资源…/…你为Cat洗了个澡</t>
+    </r>
+  </si>
+  <si>
+    <t>一瓶萤火虫</t>
+  </si>
+  <si>
+    <t>活跃于仲夏夜的小精灵。能在黑暗中发出细微的光。</t>
+  </si>
+  <si>
+    <t>有了萤火虫的陪伴，无论什么天气，你都能看见闪烁的星星。</t>
+  </si>
+  <si>
+    <t>或许你觉得让它们自由地飞行，才是更好的选择。要放生它们吗？</t>
+  </si>
+  <si>
+    <t>装有杂物的玻璃瓶</t>
+  </si>
+  <si>
+    <t>瓶如其名，装有很多小物件。</t>
+  </si>
+  <si>
+    <t>你把整个银河系都装进了玻璃瓶！！</t>
+  </si>
+  <si>
+    <t>（放置、存取物品）</t>
+  </si>
+  <si>
+    <t>邮箱</t>
+  </si>
+  <si>
+    <t>能沟通过去的小小驿站</t>
+  </si>
+  <si>
+    <t>它正在等着接受什么消息</t>
+  </si>
+  <si>
+    <t>逗猫棒</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一种奇特的小玩具，上面的羽毛貌似能吸引到</t>
     </r>
     <r>
       <rPr>
@@ -1390,6 +1870,88 @@
         <rFont val="HarmonyOS Sans SC"/>
         <charset val="134"/>
       </rPr>
+      <t>Cat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <t>人与猫语言不通，但逗猫棒往往会成为我们沟通情感的信使。</t>
+  </si>
+  <si>
+    <t>你在树下摆弄着逗猫棒……一个苹果被你吸引了。。你获得了苹果。</t>
+  </si>
+  <si>
+    <t>梳子</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>用于给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="HarmonyOS Sans SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Cat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>梳毛的工具。</t>
+    </r>
+  </si>
+  <si>
+    <t>即使是Cat，也要保持发型帅气哦。</t>
+  </si>
+  <si>
+    <t>你偷偷用这把梳子梳了自己的头发……你感觉自己的颜值更高了。</t>
+  </si>
+  <si>
+    <t>腐烂的菜品</t>
+  </si>
+  <si>
+    <t>由于长期放置而变质的菜品。（健康小提示：菜品要及时食用哦！）</t>
+  </si>
+  <si>
+    <t>不必为了腐烂的菜品而哭泣。我们要做的是珍惜还未腐烂的那些。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你吃掉了不可名状物</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="HarmonyOS Sans SC"/>
+        <charset val="134"/>
+      </rPr>
       <t>/</t>
     </r>
     <r>
@@ -1399,152 +1961,21 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>焦黄（软嫩）的烤土豆。</t>
-    </r>
-  </si>
-  <si>
-    <t>土豆总是沉默寡言，但它会将营地的温暖酿成金黄。</t>
-  </si>
-  <si>
-    <t>馒头</t>
-  </si>
-  <si>
-    <t>普通的面食，亦有乾坤。</t>
-  </si>
-  <si>
-    <t>中式无糖小面包？</t>
-  </si>
-  <si>
-    <t>米饭</t>
-  </si>
-  <si>
-    <t>生活中不可或缺的主食</t>
-  </si>
-  <si>
-    <t>雪白如玉的米粒是水稻经过时间的积淀。</t>
-  </si>
-  <si>
-    <t>苹果派（隐）</t>
-  </si>
-  <si>
-    <t>一种温馨的甜点。（完美地）融入了苹果的香气。</t>
-  </si>
-  <si>
-    <t>氤氲苹果香，和暖透心肠。</t>
-  </si>
-  <si>
-    <t>蛋糕</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>一种大号的甜品，松软醇甜（回味无穷）。/生日快乐|ू</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <charset val="134"/>
-      </rPr>
-      <t>･</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ω</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <charset val="134"/>
-      </rPr>
-      <t>･</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>` )</t>
-    </r>
-  </si>
-  <si>
-    <t>人们总会向蛋糕中注入热情与爱。这也是蛋糕甜的来源。</t>
-  </si>
-  <si>
-    <t>蘑菇炒饭（隐）</t>
-  </si>
-  <si>
-    <t>蕴含着蘑菇独特香气的炒饭。/将蘑菇的香气完美表现的炒饭</t>
-  </si>
-  <si>
-    <t>烤苹果（隐）</t>
-  </si>
-  <si>
-    <t>奇特的想法！但貌似缺少了一点什么。/奇特而美味的菜品！</t>
-  </si>
-  <si>
-    <t>偶尔的探索，也能有不错的收获。</t>
-  </si>
-  <si>
-    <t>汤（统）</t>
-  </si>
-  <si>
-    <t>鲜美的汤。（将（）的味道完美融入）</t>
-  </si>
-  <si>
-    <t>炸蘑菇</t>
-  </si>
-  <si>
-    <t>经过油炸之后变得脆脆（香脆可口）的蘑菇。</t>
-  </si>
-  <si>
-    <t>到底还有什么东西是不能炸的呢？</t>
-  </si>
-  <si>
-    <t>冷饮</t>
-  </si>
-  <si>
-    <t>夏日解暑神器！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">冰镇饮料，快乐“凉”多。 </t>
-  </si>
-  <si>
-    <t>炸小鱼</t>
-  </si>
-  <si>
-    <t>经油炸后金黄酥脆的小鱼，（焦香爽口，使味蕾激荡。）</t>
-  </si>
-  <si>
-    <t>有时厨房往往就是这么神奇，鱼只是体型不同，炸出来却完全是两种味道。</t>
-  </si>
-  <si>
-    <t>小鱼干</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>小鱼经过加工之后的产物。</t>
+      <t>腐烂的菜品。。。眼前突然一片漆黑……</t>
+    </r>
+  </si>
+  <si>
+    <t>不可名状物</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>由烹饪产生的</t>
     </r>
     <r>
       <rPr>
@@ -1553,482 +1984,6 @@
         <rFont val="HarmonyOS Sans SC"/>
         <charset val="134"/>
       </rPr>
-      <t>Cat</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>貌似很感兴趣。</t>
-    </r>
-  </si>
-  <si>
-    <t>钓上来的小鱼一定要全部做成小鱼干，然后喂给Cat！——不是Cat</t>
-  </si>
-  <si>
-    <t>你吃掉了小鱼干，咸鲜的感觉伴随着牙尖的咀嚼，扩散到了口腔的每个角落。</t>
-  </si>
-  <si>
-    <t>冰激凌</t>
-  </si>
-  <si>
-    <t>夏天最受欢迎的食品。（温馨提示：冰激凌如果不直接吃的话，还有妙用！）</t>
-  </si>
-  <si>
-    <t>在炎炎夏日中，总有一些手段，能在你的心头保留一片冬天。</t>
-  </si>
-  <si>
-    <t>你吃掉了冰激凌。舌尖涌起一阵阵甜蜜与清凉，带走了燥热与烦恼。</t>
-  </si>
-  <si>
-    <t>果盘</t>
-  </si>
-  <si>
-    <t>各种水果摆在一起，产生了一种新的美食。</t>
-  </si>
-  <si>
-    <t>果盘的特色，便是不同水果的各具特色</t>
-  </si>
-  <si>
-    <t>小蛋糕</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>简约版的蛋糕，但依旧美味。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="HarmonyOS Sans SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>但同样松软醇甜。</t>
-    </r>
-  </si>
-  <si>
-    <t>小小的蛋糕，大大的温暖。</t>
-  </si>
-  <si>
-    <t>水煮肉片</t>
-  </si>
-  <si>
-    <t>在熬煮过程中变得鲜香可口（嫩滑爽口）的肉片</t>
-  </si>
-  <si>
-    <t>古语有云，水煮肉片，水加多者为肉片汤，水加少者为滑肉。</t>
-  </si>
-  <si>
-    <t>草鱼</t>
-  </si>
-  <si>
-    <t>一种河塘中常见的鱼，也是餐桌上的常客。</t>
-  </si>
-  <si>
-    <t>草鱼貌似是位素食的狂热者。这也是它名字的由来。</t>
-  </si>
-  <si>
-    <t>或许你觉得让它在塘中漫游，才是更好的选择。要放生它吗？</t>
-  </si>
-  <si>
-    <t>鲈鱼</t>
-  </si>
-  <si>
-    <t>一种背部生有黑斑的鱼，常用于清蒸。</t>
-  </si>
-  <si>
-    <t>此行不为鲈鱼鲙，自爱名山入剡中。——李白</t>
-  </si>
-  <si>
-    <t>鲤鱼</t>
-  </si>
-  <si>
-    <t>一种被认为象征幸运的鱼。</t>
-  </si>
-  <si>
-    <t>鲤鱼对自己能带来幸运一事，同样感到幸运。</t>
-  </si>
-  <si>
-    <t>鲫鱼</t>
-  </si>
-  <si>
-    <t>一种身体比较圆润的鱼，能在汤中激发鲜香的滋味。</t>
-  </si>
-  <si>
-    <t>鲫鱼总是在塘中默默游走，随波逐流，随遇而安。</t>
-  </si>
-  <si>
-    <t>鲅鱼</t>
-  </si>
-  <si>
-    <t>一种身体细长，布有蓝色斑点的鱼，可用于包饺子。</t>
-  </si>
-  <si>
-    <t>鲅鱼可是名副其实的旅行家，它的目标可不止一片小塘。</t>
-  </si>
-  <si>
-    <t>小黄鱼</t>
-  </si>
-  <si>
-    <t>一种小小的金黄色的鱼，适配各种烹饪方法。</t>
-  </si>
-  <si>
-    <t>小黄鱼往往身居水底，却把自己活成了金色的阳光。</t>
-  </si>
-  <si>
-    <t>石斑鱼</t>
-  </si>
-  <si>
-    <t>其貌不扬，味道却很突出。</t>
-  </si>
-  <si>
-    <t>不要小看石斑鱼的外貌。这也是它捕猎的手段之一。</t>
-  </si>
-  <si>
-    <t>鲳鱼</t>
-  </si>
-  <si>
-    <t>一种身体扁扁的大头鱼。</t>
-  </si>
-  <si>
-    <t>鲳鱼又在用它的大脑袋思考什么呢？</t>
-  </si>
-  <si>
-    <t>带鱼</t>
-  </si>
-  <si>
-    <t>一种身体很长的鱼，常用于红烧。</t>
-  </si>
-  <si>
-    <t>希望你每天笑脸“长”在。（There's no need to keep your face long.）</t>
-  </si>
-  <si>
-    <t>河豚</t>
-  </si>
-  <si>
-    <t>一种会变得圆滚滚的鱼。（温馨提示：非专业人士谨慎烹饪！）</t>
-  </si>
-  <si>
-    <t>美味的诱惑，有时也伴随着致命的风险。</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>一种神奇的鱼，周身散发着微弱的幽蓝。</t>
-  </si>
-  <si>
-    <t>其他鱼类往往对青鱼总喜欢像幽灵一样，深居水塘内部感到奇怪。其实，它只是将自己的内心套上了一层保护色。</t>
-  </si>
-  <si>
-    <t>河虾</t>
-  </si>
-  <si>
-    <t>隐匿于浅塘中的节肢动物。</t>
-  </si>
-  <si>
-    <t>河虾总自认为是水塘中的神秘侠客。它们习惯隐藏自己，在夜晚才开始一天的生活。</t>
-  </si>
-  <si>
-    <t>鲦鱼</t>
-  </si>
-  <si>
-    <t>一种活泼敏捷的小鱼。</t>
-  </si>
-  <si>
-    <t>鲦鱼出游从容，是鱼之乐也。——《庄子》</t>
-  </si>
-  <si>
-    <t>水草</t>
-  </si>
-  <si>
-    <t>一种水生藻类植物，虽然营养价值极高，但经常被人们忽视。</t>
-  </si>
-  <si>
-    <t>水草不是垃圾，它在餐桌上的价值可不比鱼类差！</t>
-  </si>
-  <si>
-    <t>玻璃瓶</t>
-  </si>
-  <si>
-    <t>曾经装过信纸的玻璃瓶。或许可以用它干点什么有意思的事……</t>
-  </si>
-  <si>
-    <t>玻璃瓶很小，但却能大到容纳世间一切浪漫。</t>
-  </si>
-  <si>
-    <t>（装东西）</t>
-  </si>
-  <si>
-    <t>一朵花</t>
-  </si>
-  <si>
-    <t>曾经生长在大自然中的植物，现在正在玻璃瓶中静静绽放。</t>
-  </si>
-  <si>
-    <t>今天也要保持绽放哦！</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="HarmonyOS Sans SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>可放置。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="HarmonyOS Sans SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你看到这朵花仍在绽放，心情舒畅了许多。</t>
-    </r>
-  </si>
-  <si>
-    <t>一瓶水</t>
-  </si>
-  <si>
-    <t>生命生长的必要物资。</t>
-  </si>
-  <si>
-    <t>生命的奇迹便源于这种普通的物质。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你喝掉了水。一股清凉透过你的心尖。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="HarmonyOS Sans SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你为农作物浇了水。。幼苗经过你的洗礼，生长得更旺盛了。但你或许应该用你的水壶。/…你为水塘补充了水资源…/…你为Cat洗了个澡</t>
-    </r>
-  </si>
-  <si>
-    <t>一瓶萤火虫</t>
-  </si>
-  <si>
-    <t>活跃于仲夏夜的小精灵。能在黑暗中发出细微的光。</t>
-  </si>
-  <si>
-    <t>有了萤火虫的陪伴，无论什么天气，你都能看见闪烁的星星。</t>
-  </si>
-  <si>
-    <t>或许你觉得让它们自由地飞行，才是更好的选择。要放生它们吗？</t>
-  </si>
-  <si>
-    <t>装有杂物的玻璃瓶</t>
-  </si>
-  <si>
-    <t>瓶如其名，装有很多小物件。</t>
-  </si>
-  <si>
-    <t>你把整个银河系都装进了玻璃瓶！！</t>
-  </si>
-  <si>
-    <t>（放置、存取物品）</t>
-  </si>
-  <si>
-    <t>邮箱</t>
-  </si>
-  <si>
-    <t>能沟通过去的小小驿站</t>
-  </si>
-  <si>
-    <t>它正在等着接受什么消息</t>
-  </si>
-  <si>
-    <t>逗猫棒</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>一种奇特的小玩具，上面的羽毛貌似能吸引到</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="HarmonyOS Sans SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Cat</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <t>人与猫语言不通，但逗猫棒往往会成为我们沟通情感的信使。</t>
-  </si>
-  <si>
-    <t>你在树下摆弄着逗猫棒……一个苹果被你吸引了。。你获得了苹果。</t>
-  </si>
-  <si>
-    <t>梳子</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>用于给</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="HarmonyOS Sans SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Cat</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>梳毛的工具。</t>
-    </r>
-  </si>
-  <si>
-    <t>即使是Cat，也要保持发型帅气哦。</t>
-  </si>
-  <si>
-    <t>你偷偷用这把梳子梳了自己的头发……你感觉自己的颜值更高了。</t>
-  </si>
-  <si>
-    <t>腐烂的菜品</t>
-  </si>
-  <si>
-    <t>由于长期放置而变质的菜品。（健康小提示：菜品要及时食用哦！）</t>
-  </si>
-  <si>
-    <t>不必为了腐烂的菜品而哭泣。我们要做的是珍惜还未腐烂的那些。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你吃掉了不可名状物</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="HarmonyOS Sans SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>腐烂的菜品。。。眼前突然一片漆黑……</t>
-    </r>
-  </si>
-  <si>
-    <t>不可名状物</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>由烹饪产生的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="HarmonyOS Sans SC"/>
-        <charset val="134"/>
-      </rPr>
       <t>“</t>
     </r>
     <r>
@@ -2102,15 +2057,12 @@
     <t>本水塘生活手册</t>
   </si>
   <si>
-    <t>记载了本水塘生活的所有的技巧</t>
+    <t>记载了本水塘生活的一些技巧。</t>
   </si>
   <si>
     <t>生活的技巧可以传授，但生活的智慧只能由自己体悟。</t>
   </si>
   <si>
-    <t>（打开）（另附文件）</t>
-  </si>
-  <si>
     <t>番茄种子</t>
   </si>
   <si>
@@ -2142,6 +2094,18 @@
   </si>
   <si>
     <t>西瓜种子</t>
+  </si>
+  <si>
+    <t>草</t>
+  </si>
+  <si>
+    <t>一株纤细的小草，貌似扎根很深。/一株很高的草。它会不会长到树那么高呢？</t>
+  </si>
+  <si>
+    <t>竹子</t>
+  </si>
+  <si>
+    <t>一株长到树那么高的草。好吧，这叫竹子。☞一棵竹子，很有韧性。</t>
   </si>
 </sst>
 </file>
@@ -2787,7 +2751,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2843,15 +2807,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3176,7 +3137,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="18.4818181818182" style="1" customWidth="1"/>
@@ -3558,7 +3519,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="33" ht="84" spans="1:4">
+    <row r="33" ht="42" spans="1:4">
       <c r="A33" s="3" t="s">
         <v>100</v>
       </c>
@@ -3822,39 +3783,39 @@
       <c r="B53" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" t="s">
         <v>174</v>
       </c>
-      <c r="D53" s="16" t="s">
+      <c r="D53" s="18" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" ht="28" spans="1:4">
       <c r="A54" s="2" t="s">
         <v>176</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="12" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="55" ht="42" spans="1:4">
+      <c r="D54" s="16" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C55" t="s">
-        <v>181</v>
-      </c>
-      <c r="D55" s="16" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" ht="42" spans="1:4">
       <c r="A56" s="2" t="s">
         <v>183</v>
       </c>
@@ -3864,7 +3825,7 @@
       <c r="C56" t="s">
         <v>185</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" s="16" t="s">
         <v>186</v>
       </c>
     </row>
@@ -3878,75 +3839,75 @@
       <c r="C57" t="s">
         <v>189</v>
       </c>
-      <c r="D57" s="2"/>
+      <c r="D57" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C58" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D58" s="2"/>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C59" t="s">
-        <v>195</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="D59" s="2"/>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C60" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="61" ht="28" spans="1:4">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
       <c r="A61" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C61" s="12" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="62" spans="1:4">
+      <c r="C61" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="62" ht="28" spans="1:4">
       <c r="A62" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C62" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="63" ht="28" spans="1:4">
+      <c r="C62" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
       <c r="A63" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B63" s="16" t="s">
         <v>206</v>
       </c>
+      <c r="B63" s="2" t="s">
+        <v>207</v>
+      </c>
       <c r="C63" t="s">
-        <v>207</v>
-      </c>
-      <c r="D63" s="18" t="s">
         <v>208</v>
       </c>
     </row>
@@ -3954,37 +3915,37 @@
       <c r="A64" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" t="s">
         <v>211</v>
       </c>
-      <c r="D64" s="18"/>
-    </row>
-    <row r="65" spans="1:4">
+      <c r="D64" s="19"/>
+    </row>
+    <row r="65" ht="28" spans="1:4">
       <c r="A65" s="2" t="s">
         <v>212</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="D65" s="18"/>
-    </row>
-    <row r="66" ht="28" spans="1:4">
+      <c r="D65" s="19"/>
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B66" s="16" t="s">
+      <c r="B66" s="2" t="s">
         <v>216</v>
       </c>
       <c r="C66" t="s">
         <v>217</v>
       </c>
-      <c r="D66" s="18"/>
+      <c r="D66" s="19"/>
     </row>
     <row r="67" ht="28" spans="1:4">
       <c r="A67" s="2" t="s">
@@ -3996,7 +3957,7 @@
       <c r="C67" t="s">
         <v>220</v>
       </c>
-      <c r="D67" s="18"/>
+      <c r="D67" s="19"/>
     </row>
     <row r="68" ht="28" spans="1:4">
       <c r="A68" s="2" t="s">
@@ -4008,19 +3969,19 @@
       <c r="C68" t="s">
         <v>223</v>
       </c>
-      <c r="D68" s="18"/>
-    </row>
-    <row r="69" spans="1:4">
+      <c r="D68" s="19"/>
+    </row>
+    <row r="69" ht="28" spans="1:4">
       <c r="A69" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="16" t="s">
         <v>225</v>
       </c>
       <c r="C69" t="s">
         <v>226</v>
       </c>
-      <c r="D69" s="18"/>
+      <c r="D69" s="19"/>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2" t="s">
@@ -4032,7 +3993,7 @@
       <c r="C70" t="s">
         <v>229</v>
       </c>
-      <c r="D70" s="18"/>
+      <c r="D70" s="19"/>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2" t="s">
@@ -4044,7 +4005,7 @@
       <c r="C71" t="s">
         <v>232</v>
       </c>
-      <c r="D71" s="18"/>
+      <c r="D71" s="19"/>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2" t="s">
@@ -4056,21 +4017,21 @@
       <c r="C72" t="s">
         <v>235</v>
       </c>
-      <c r="D72" s="18"/>
-    </row>
-    <row r="73" ht="28" spans="1:4">
+      <c r="D72" s="19"/>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B73" s="16" t="s">
+      <c r="B73" s="2" t="s">
         <v>237</v>
       </c>
       <c r="C73" t="s">
         <v>238</v>
       </c>
-      <c r="D73" s="18"/>
-    </row>
-    <row r="74" spans="1:4">
+      <c r="D73" s="19"/>
+    </row>
+    <row r="74" ht="28" spans="1:4">
       <c r="A74" s="2" t="s">
         <v>239</v>
       </c>
@@ -4080,31 +4041,31 @@
       <c r="C74" t="s">
         <v>241</v>
       </c>
-      <c r="D74" s="18"/>
-    </row>
-    <row r="75" ht="28" spans="1:4">
+      <c r="D74" s="19"/>
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C75" t="s">
         <v>244</v>
       </c>
-      <c r="D75" s="18"/>
-    </row>
-    <row r="76" spans="1:4">
+      <c r="D75" s="19"/>
+    </row>
+    <row r="76" ht="28" spans="1:4">
       <c r="A76" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B76" s="16" t="s">
+      <c r="B76" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="D76" s="18"/>
+      <c r="D76" s="19"/>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2" t="s">
@@ -4116,43 +4077,43 @@
       <c r="C77" t="s">
         <v>250</v>
       </c>
-      <c r="D77" s="18"/>
+      <c r="D77" s="19"/>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="C78" t="s">
         <v>253</v>
       </c>
-      <c r="D78" s="18"/>
-    </row>
-    <row r="79" ht="28" spans="1:4">
+      <c r="D78" s="19"/>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B79" s="16" t="s">
+      <c r="B79" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="D79" s="18"/>
-    </row>
-    <row r="80" spans="1:4">
+      <c r="D79" s="19"/>
+    </row>
+    <row r="80" ht="28" spans="1:4">
       <c r="A80" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="16" t="s">
         <v>258</v>
       </c>
       <c r="C80" t="s">
         <v>259</v>
       </c>
-      <c r="D80" s="18"/>
+      <c r="D80" s="19"/>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2" t="s">
@@ -4162,33 +4123,33 @@
         <v>261</v>
       </c>
       <c r="C81" t="s">
-        <v>238</v>
-      </c>
-      <c r="D81" s="18"/>
+        <v>262</v>
+      </c>
+      <c r="D81" s="19"/>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B82" s="16" t="s">
         <v>263</v>
       </c>
+      <c r="B82" s="2" t="s">
+        <v>264</v>
+      </c>
       <c r="C82" t="s">
-        <v>264</v>
-      </c>
-      <c r="D82" s="18"/>
+        <v>241</v>
+      </c>
+      <c r="D82" s="19"/>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="16" t="s">
         <v>266</v>
       </c>
       <c r="C83" t="s">
         <v>267</v>
       </c>
-      <c r="D83" s="18"/>
+      <c r="D83" s="19"/>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2" t="s">
@@ -4200,7 +4161,7 @@
       <c r="C84" t="s">
         <v>270</v>
       </c>
-      <c r="D84" s="18"/>
+      <c r="D84" s="19"/>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2" t="s">
@@ -4212,7 +4173,7 @@
       <c r="C85" t="s">
         <v>273</v>
       </c>
-      <c r="D85" s="18"/>
+      <c r="D85" s="19"/>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2" t="s">
@@ -4224,122 +4185,122 @@
       <c r="C86" t="s">
         <v>276</v>
       </c>
-      <c r="D86" s="18"/>
+      <c r="D86" s="19" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C87" t="s">
-        <v>279</v>
-      </c>
-      <c r="D87" s="18"/>
-    </row>
-    <row r="88" ht="16.5" spans="1:4">
+        <v>280</v>
+      </c>
+      <c r="D87" s="19"/>
+    </row>
+    <row r="88" spans="1:4">
       <c r="A88" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="B88" s="16" t="s">
         <v>281</v>
       </c>
+      <c r="B88" s="2" t="s">
+        <v>282</v>
+      </c>
       <c r="C88" t="s">
-        <v>282</v>
-      </c>
-      <c r="D88" s="18"/>
-    </row>
-    <row r="89" spans="1:4">
+        <v>283</v>
+      </c>
+      <c r="D88" s="19"/>
+    </row>
+    <row r="89" ht="16.5" spans="1:4">
       <c r="A89" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="B89" s="2" t="s">
         <v>284</v>
       </c>
+      <c r="B89" s="16" t="s">
+        <v>285</v>
+      </c>
       <c r="C89" t="s">
-        <v>267</v>
-      </c>
-      <c r="D89" s="18"/>
+        <v>286</v>
+      </c>
+      <c r="D89" s="19"/>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C90" t="s">
-        <v>287</v>
-      </c>
-      <c r="D90" s="18"/>
-    </row>
-    <row r="91" ht="28" spans="1:4">
+        <v>270</v>
+      </c>
+      <c r="D90" s="19"/>
+    </row>
+    <row r="91" spans="1:4">
       <c r="A91" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C91" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="D91" s="18"/>
-    </row>
-    <row r="92" spans="1:4">
+        <v>290</v>
+      </c>
+      <c r="C91" t="s">
+        <v>291</v>
+      </c>
+      <c r="D91" s="19"/>
+    </row>
+    <row r="92" ht="28" spans="1:4">
       <c r="A92" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C92" t="s">
-        <v>292</v>
-      </c>
-      <c r="D92" s="18"/>
+        <v>293</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="D92" s="19"/>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C93" t="s">
-        <v>295</v>
-      </c>
-      <c r="D93" s="18"/>
+        <v>296</v>
+      </c>
+      <c r="D93" s="19"/>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C94" t="s">
-        <v>298</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="D94" s="19"/>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C95" t="s">
-        <v>301</v>
-      </c>
-      <c r="D95" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="96" ht="28" spans="1:4">
+    <row r="96" spans="1:4">
       <c r="A96" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B96" s="16" t="s">
+      <c r="B96" s="2" t="s">
         <v>304</v>
       </c>
       <c r="C96" t="s">
@@ -4349,510 +4310,540 @@
         <v>306</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" ht="28" spans="1:4">
       <c r="A97" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B97" s="16" t="s">
         <v>308</v>
       </c>
       <c r="C97" t="s">
         <v>309</v>
       </c>
+      <c r="D97" s="16" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C98" t="s">
-        <v>312</v>
+        <v>313</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C99" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C100" t="s">
-        <v>318</v>
-      </c>
-      <c r="D100" s="16" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C101" t="s">
-        <v>322</v>
-      </c>
-      <c r="D101" s="16"/>
+        <v>323</v>
+      </c>
+      <c r="D101" s="16" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C102" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D102" s="16"/>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C103" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D103" s="16"/>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C104" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D104" s="16"/>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C105" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D105" s="16"/>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C106" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D106" s="16"/>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C107" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D107" s="16"/>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C108" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D108" s="16"/>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C109" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D109" s="16"/>
     </row>
-    <row r="110" ht="28" spans="1:4">
+    <row r="110" spans="1:4">
       <c r="A110" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="C110" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
+      </c>
+      <c r="C110" t="s">
+        <v>351</v>
       </c>
       <c r="D110" s="16"/>
     </row>
-    <row r="111" spans="1:4">
+    <row r="111" ht="28" spans="1:4">
       <c r="A111" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C111" t="s">
-        <v>352</v>
+        <v>353</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>354</v>
       </c>
       <c r="D111" s="16"/>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C112" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D112" s="16"/>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C113" t="s">
-        <v>358</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="D113" s="16"/>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>362</v>
       </c>
       <c r="C114" t="s">
-        <v>361</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="B115" s="2" t="s">
         <v>364</v>
       </c>
+      <c r="B115" s="1" t="s">
+        <v>365</v>
+      </c>
       <c r="C115" t="s">
-        <v>365</v>
-      </c>
-      <c r="D115" s="1" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="116" ht="42" spans="1:4">
+      <c r="D115" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
       <c r="A116" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C116" t="s">
-        <v>369</v>
-      </c>
-      <c r="D116" s="16" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="117" spans="1:4">
+      <c r="D116" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="117" ht="42" spans="1:4">
       <c r="A117" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C117" t="s">
-        <v>373</v>
-      </c>
-      <c r="D117" s="2" t="s">
         <v>374</v>
+      </c>
+      <c r="D117" s="16" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C118" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="119" spans="1:4">
-      <c r="A119" s="3" t="s">
-        <v>379</v>
+      <c r="A119" s="2" t="s">
+        <v>380</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
+      </c>
+      <c r="C119" t="s">
+        <v>382</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
-      <c r="A120" s="2" t="s">
-        <v>382</v>
+      <c r="A120" s="3" t="s">
+        <v>384</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="C120" s="12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="C121" t="s">
         <v>388</v>
       </c>
+      <c r="C121" s="12" t="s">
+        <v>389</v>
+      </c>
       <c r="D121" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C122" t="s">
-        <v>392</v>
-      </c>
-      <c r="D122" s="19" t="s">
         <v>393</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C123" t="s">
-        <v>396</v>
-      </c>
-      <c r="D123" s="19"/>
+        <v>397</v>
+      </c>
+      <c r="D123" s="16" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>399</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="C124" t="s">
+        <v>401</v>
+      </c>
+      <c r="D124" s="16"/>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="C125" s="5"/>
+        <v>403</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C126" s="5"/>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C127" s="5"/>
     </row>
     <row r="128" spans="1:4">
-      <c r="A128" s="3" t="s">
-        <v>406</v>
+      <c r="A128" s="2" t="s">
+        <v>409</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C128" s="5"/>
     </row>
     <row r="129" spans="1:4">
-      <c r="A129" s="2" t="s">
-        <v>408</v>
+      <c r="A129" s="3" t="s">
+        <v>411</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="C129" t="s">
-        <v>410</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>411</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="C129" s="5"/>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C130" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B131" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C131" t="s">
+        <v>419</v>
+      </c>
+      <c r="D131" s="2" t="s">
         <v>416</v>
-      </c>
-      <c r="C131" t="s">
-        <v>417</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="B132" s="20" t="s">
         <v>420</v>
       </c>
-      <c r="C132" s="21" t="s">
+      <c r="B132" s="2" t="s">
         <v>421</v>
+      </c>
+      <c r="C132" t="s">
+        <v>422</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="B133" s="22"/>
-      <c r="C133" s="21"/>
+        <v>423</v>
+      </c>
+      <c r="B133" s="20" t="s">
+        <v>424</v>
+      </c>
+      <c r="C133" s="10" t="s">
+        <v>425</v>
+      </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="B134" s="22"/>
-      <c r="C134" s="21"/>
+        <v>426</v>
+      </c>
+      <c r="B134" s="21"/>
+      <c r="C134" s="10"/>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="B135" s="22"/>
-      <c r="C135" s="21"/>
+        <v>427</v>
+      </c>
+      <c r="B135" s="21"/>
+      <c r="C135" s="10"/>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="B136" s="22"/>
-      <c r="C136" s="21"/>
+        <v>428</v>
+      </c>
+      <c r="B136" s="21"/>
+      <c r="C136" s="10"/>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="B137" s="22"/>
-      <c r="C137" s="21"/>
+        <v>429</v>
+      </c>
+      <c r="B137" s="21"/>
+      <c r="C137" s="10"/>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="B138" s="22"/>
-      <c r="C138" s="21"/>
+        <v>430</v>
+      </c>
+      <c r="B138" s="21"/>
+      <c r="C138" s="10"/>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="B139" s="22"/>
-      <c r="C139" s="21"/>
+        <v>431</v>
+      </c>
+      <c r="B139" s="21"/>
+      <c r="C139" s="10"/>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="B140" s="22"/>
-      <c r="C140" s="21"/>
+        <v>432</v>
+      </c>
+      <c r="B140" s="21"/>
+      <c r="C140" s="10"/>
     </row>
     <row r="141" spans="1:4">
-      <c r="C141" s="21"/>
+      <c r="A141" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B141" s="21"/>
+      <c r="C141" s="10"/>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C142" s="5"/>
+      <c r="D142" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>437</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B132:B140"/>
+  <mergeCells count="5">
+    <mergeCell ref="B133:B141"/>
     <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C132:C141"/>
+    <mergeCell ref="C133:C141"/>
     <mergeCell ref="D4:D7"/>
     <mergeCell ref="D20:D22"/>
-    <mergeCell ref="D63:D93"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/docs/game/items-zh_CN.xlsx
+++ b/docs/game/items-zh_CN.xlsx
@@ -883,6 +883,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>你吃掉了橙子。酸甜的汁水从饱满的果粒中炸开，涌进嘴里。</t>
     </r>
     <r>
@@ -1589,7 +1595,7 @@
     <t>在熬煮过程中变得鲜香可口（嫩滑爽口）的肉片</t>
   </si>
   <si>
-    <t>古语有云，水煮肉片，水加多者为肉片汤，水加少者为滑肉。</t>
+    <t>人生应由自己“煮”导！</t>
   </si>
   <si>
     <t>草鱼</t>
@@ -2751,7 +2757,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2805,9 +2811,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3786,7 +3789,7 @@
       <c r="C53" t="s">
         <v>174</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="D53" s="16" t="s">
         <v>175</v>
       </c>
     </row>
@@ -3921,7 +3924,7 @@
       <c r="C64" t="s">
         <v>211</v>
       </c>
-      <c r="D64" s="19"/>
+      <c r="D64" s="18"/>
     </row>
     <row r="65" ht="28" spans="1:4">
       <c r="A65" s="2" t="s">
@@ -3933,7 +3936,7 @@
       <c r="C65" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="D65" s="19"/>
+      <c r="D65" s="18"/>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2" t="s">
@@ -3945,7 +3948,7 @@
       <c r="C66" t="s">
         <v>217</v>
       </c>
-      <c r="D66" s="19"/>
+      <c r="D66" s="18"/>
     </row>
     <row r="67" ht="28" spans="1:4">
       <c r="A67" s="2" t="s">
@@ -3957,7 +3960,7 @@
       <c r="C67" t="s">
         <v>220</v>
       </c>
-      <c r="D67" s="19"/>
+      <c r="D67" s="18"/>
     </row>
     <row r="68" ht="28" spans="1:4">
       <c r="A68" s="2" t="s">
@@ -3969,7 +3972,7 @@
       <c r="C68" t="s">
         <v>223</v>
       </c>
-      <c r="D68" s="19"/>
+      <c r="D68" s="18"/>
     </row>
     <row r="69" ht="28" spans="1:4">
       <c r="A69" s="2" t="s">
@@ -3981,7 +3984,7 @@
       <c r="C69" t="s">
         <v>226</v>
       </c>
-      <c r="D69" s="19"/>
+      <c r="D69" s="18"/>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2" t="s">
@@ -3993,7 +3996,7 @@
       <c r="C70" t="s">
         <v>229</v>
       </c>
-      <c r="D70" s="19"/>
+      <c r="D70" s="18"/>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2" t="s">
@@ -4005,7 +4008,7 @@
       <c r="C71" t="s">
         <v>232</v>
       </c>
-      <c r="D71" s="19"/>
+      <c r="D71" s="18"/>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2" t="s">
@@ -4017,7 +4020,7 @@
       <c r="C72" t="s">
         <v>235</v>
       </c>
-      <c r="D72" s="19"/>
+      <c r="D72" s="18"/>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2" t="s">
@@ -4029,7 +4032,7 @@
       <c r="C73" t="s">
         <v>238</v>
       </c>
-      <c r="D73" s="19"/>
+      <c r="D73" s="18"/>
     </row>
     <row r="74" ht="28" spans="1:4">
       <c r="A74" s="2" t="s">
@@ -4041,7 +4044,7 @@
       <c r="C74" t="s">
         <v>241</v>
       </c>
-      <c r="D74" s="19"/>
+      <c r="D74" s="18"/>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2" t="s">
@@ -4053,7 +4056,7 @@
       <c r="C75" t="s">
         <v>244</v>
       </c>
-      <c r="D75" s="19"/>
+      <c r="D75" s="18"/>
     </row>
     <row r="76" ht="28" spans="1:4">
       <c r="A76" s="2" t="s">
@@ -4065,7 +4068,7 @@
       <c r="C76" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="D76" s="19"/>
+      <c r="D76" s="18"/>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2" t="s">
@@ -4077,7 +4080,7 @@
       <c r="C77" t="s">
         <v>250</v>
       </c>
-      <c r="D77" s="19"/>
+      <c r="D77" s="18"/>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2" t="s">
@@ -4089,7 +4092,7 @@
       <c r="C78" t="s">
         <v>253</v>
       </c>
-      <c r="D78" s="19"/>
+      <c r="D78" s="18"/>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2" t="s">
@@ -4101,7 +4104,7 @@
       <c r="C79" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="D79" s="19"/>
+      <c r="D79" s="18"/>
     </row>
     <row r="80" ht="28" spans="1:4">
       <c r="A80" s="2" t="s">
@@ -4113,7 +4116,7 @@
       <c r="C80" t="s">
         <v>259</v>
       </c>
-      <c r="D80" s="19"/>
+      <c r="D80" s="18"/>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2" t="s">
@@ -4125,7 +4128,7 @@
       <c r="C81" t="s">
         <v>262</v>
       </c>
-      <c r="D81" s="19"/>
+      <c r="D81" s="18"/>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2" t="s">
@@ -4137,7 +4140,7 @@
       <c r="C82" t="s">
         <v>241</v>
       </c>
-      <c r="D82" s="19"/>
+      <c r="D82" s="18"/>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2" t="s">
@@ -4149,7 +4152,7 @@
       <c r="C83" t="s">
         <v>267</v>
       </c>
-      <c r="D83" s="19"/>
+      <c r="D83" s="18"/>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2" t="s">
@@ -4161,7 +4164,7 @@
       <c r="C84" t="s">
         <v>270</v>
       </c>
-      <c r="D84" s="19"/>
+      <c r="D84" s="18"/>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2" t="s">
@@ -4173,7 +4176,7 @@
       <c r="C85" t="s">
         <v>273</v>
       </c>
-      <c r="D85" s="19"/>
+      <c r="D85" s="18"/>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2" t="s">
@@ -4185,7 +4188,7 @@
       <c r="C86" t="s">
         <v>276</v>
       </c>
-      <c r="D86" s="19" t="s">
+      <c r="D86" s="18" t="s">
         <v>277</v>
       </c>
     </row>
@@ -4199,7 +4202,7 @@
       <c r="C87" t="s">
         <v>280</v>
       </c>
-      <c r="D87" s="19"/>
+      <c r="D87" s="18"/>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2" t="s">
@@ -4211,7 +4214,7 @@
       <c r="C88" t="s">
         <v>283</v>
       </c>
-      <c r="D88" s="19"/>
+      <c r="D88" s="18"/>
     </row>
     <row r="89" ht="16.5" spans="1:4">
       <c r="A89" s="2" t="s">
@@ -4223,7 +4226,7 @@
       <c r="C89" t="s">
         <v>286</v>
       </c>
-      <c r="D89" s="19"/>
+      <c r="D89" s="18"/>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2" t="s">
@@ -4235,7 +4238,7 @@
       <c r="C90" t="s">
         <v>270</v>
       </c>
-      <c r="D90" s="19"/>
+      <c r="D90" s="18"/>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2" t="s">
@@ -4247,7 +4250,7 @@
       <c r="C91" t="s">
         <v>291</v>
       </c>
-      <c r="D91" s="19"/>
+      <c r="D91" s="18"/>
     </row>
     <row r="92" ht="28" spans="1:4">
       <c r="A92" s="2" t="s">
@@ -4259,7 +4262,7 @@
       <c r="C92" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="D92" s="19"/>
+      <c r="D92" s="18"/>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2" t="s">
@@ -4271,7 +4274,7 @@
       <c r="C93" t="s">
         <v>296</v>
       </c>
-      <c r="D93" s="19"/>
+      <c r="D93" s="18"/>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2" t="s">
@@ -4283,7 +4286,7 @@
       <c r="C94" t="s">
         <v>299</v>
       </c>
-      <c r="D94" s="19"/>
+      <c r="D94" s="18"/>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2" t="s">
@@ -4757,7 +4760,7 @@
       <c r="A133" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B133" s="20" t="s">
+      <c r="B133" s="19" t="s">
         <v>424</v>
       </c>
       <c r="C133" s="10" t="s">
@@ -4768,56 +4771,56 @@
       <c r="A134" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="B134" s="21"/>
+      <c r="B134" s="20"/>
       <c r="C134" s="10"/>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B135" s="21"/>
+      <c r="B135" s="20"/>
       <c r="C135" s="10"/>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="B136" s="21"/>
+      <c r="B136" s="20"/>
       <c r="C136" s="10"/>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B137" s="21"/>
+      <c r="B137" s="20"/>
       <c r="C137" s="10"/>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="B138" s="21"/>
+      <c r="B138" s="20"/>
       <c r="C138" s="10"/>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B139" s="21"/>
+      <c r="B139" s="20"/>
       <c r="C139" s="10"/>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="B140" s="21"/>
+      <c r="B140" s="20"/>
       <c r="C140" s="10"/>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="B141" s="21"/>
+      <c r="B141" s="20"/>
       <c r="C141" s="10"/>
     </row>
     <row r="142" spans="1:4">
